--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -496,6 +496,88 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HDV</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>154</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.195</v>
+      </c>
+      <c r="F2" t="n">
+        <v>80</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>increase toward target 15% of capital (core)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>69</v>
+      </c>
+      <c r="E3" t="n">
+        <v>65.145</v>
+      </c>
+      <c r="F3" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>increase toward target 15% of capital (core)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDV</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -513,13 +513,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="E2" t="n">
-        <v>29.195</v>
+        <v>65.145</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>HDV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>69</v>
+        <v>152</v>
       </c>
       <c r="E3" t="n">
-        <v>65.145</v>
+        <v>29.195</v>
       </c>
       <c r="F3" t="n">
-        <v>75.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -571,6 +571,9 @@
         <is>
           <t>2026-08-17T13:32:55.671253+00:00</t>
         </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0.8100000000000094</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>HDV</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -513,13 +513,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
+        <v>150</v>
       </c>
       <c r="E2" t="n">
-        <v>65.145</v>
+        <v>29.195</v>
       </c>
       <c r="F2" t="n">
-        <v>75.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -530,6 +530,9 @@
         <is>
           <t>2026-08-17T13:32:55.671253+00:00</t>
         </is>
+      </c>
+      <c r="K2" t="n">
+        <v>2.300000000000018</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -540,7 +543,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDV</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,13 +557,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>152</v>
+        <v>68</v>
       </c>
       <c r="E3" t="n">
-        <v>29.195</v>
+        <v>65.145</v>
       </c>
       <c r="F3" t="n">
-        <v>80</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -573,7 +576,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.8100000000000094</v>
+        <v>0.6200000000000045</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E3" t="n">
-        <v>65.145</v>
+        <v>65.14724637681159</v>
       </c>
       <c r="F3" t="n">
         <v>75.09999999999999</v>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDV</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -513,13 +513,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>150</v>
+        <v>69</v>
       </c>
       <c r="E2" t="n">
-        <v>29.195</v>
+        <v>65.14724637681159</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.300000000000018</v>
+        <v>0.6200000000000045</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>HDV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>69</v>
+        <v>151</v>
       </c>
       <c r="E3" t="n">
-        <v>65.14724637681159</v>
+        <v>29.19933774834437</v>
       </c>
       <c r="F3" t="n">
-        <v>75.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.6200000000000045</v>
+        <v>2.300000000000018</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>HDV</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -513,13 +513,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
+        <v>151</v>
       </c>
       <c r="E2" t="n">
-        <v>65.14724637681159</v>
+        <v>29.19933774834437</v>
       </c>
       <c r="F2" t="n">
-        <v>75.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.6200000000000045</v>
+        <v>2.300000000000018</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDV</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>151</v>
+        <v>68</v>
       </c>
       <c r="E3" t="n">
-        <v>29.19933774834437</v>
+        <v>65.14724637681159</v>
       </c>
       <c r="F3" t="n">
-        <v>80</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2.300000000000018</v>
+        <v>1.452753623188414</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E3" t="n">
         <v>65.14724637681159</v>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1.452753623188414</v>
+        <v>3.135507246376818</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDV</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -513,13 +513,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>151</v>
+        <v>67</v>
       </c>
       <c r="E2" t="n">
-        <v>29.19933774834437</v>
+        <v>65.14724637681159</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.300000000000018</v>
+        <v>3.135507246376818</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>HDV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="E3" t="n">
-        <v>65.14724637681159</v>
+        <v>29.20322368421052</v>
       </c>
       <c r="F3" t="n">
-        <v>75.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3.135507246376818</v>
+        <v>2.300000000000018</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>HDV</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -513,13 +513,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>67</v>
+        <v>154</v>
       </c>
       <c r="E2" t="n">
-        <v>65.14724637681159</v>
+        <v>29.20720779220779</v>
       </c>
       <c r="F2" t="n">
-        <v>75.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3.135507246376818</v>
+        <v>2.300000000000018</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDV</t>
+          <t>JEPI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="E3" t="n">
-        <v>29.20322368421052</v>
+        <v>57.355</v>
       </c>
       <c r="F3" t="n">
-        <v>80</v>
+        <v>71.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -572,13 +572,54 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>2026-09-04T13:35:33.221049+00:00</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>increase toward target 15% of capital (core)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>65</v>
+      </c>
+      <c r="E4" t="n">
+        <v>65.14724637681159</v>
+      </c>
+      <c r="F4" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>2026-08-17T13:32:55.671253+00:00</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>2.300000000000018</v>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="K4" t="n">
+        <v>12.08101449275364</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>increase toward target 15% of capital (core)</t>
         </is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDV</t>
+          <t>JEPI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -513,13 +513,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>154</v>
+        <v>79</v>
       </c>
       <c r="E2" t="n">
-        <v>29.20720779220779</v>
+        <v>57.355</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>71.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -528,11 +528,8 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-17T13:32:55.671253+00:00</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>2.300000000000018</v>
+          <t>2026-09-04T13:35:33.221049+00:00</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -543,7 +540,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JEPI</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -557,13 +554,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E3" t="n">
-        <v>57.355</v>
+        <v>65.14724637681159</v>
       </c>
       <c r="F3" t="n">
-        <v>71.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -572,8 +569,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-04T13:35:33.221049+00:00</t>
-        </is>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>12.08101449275364</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>HDV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -598,17 +598,17 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>65</v>
+        <v>154</v>
       </c>
       <c r="E4" t="n">
-        <v>65.14724637681159</v>
+        <v>29.20720779220779</v>
       </c>
       <c r="F4" t="n">
-        <v>75.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -616,8 +616,16 @@
           <t>2026-08-17T13:32:55.671253+00:00</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:35:49.546017+00:00</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>29.28419999999999</v>
+      </c>
       <c r="K4" t="n">
-        <v>12.08101449275364</v>
+        <v>14.15679999999965</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -540,7 +540,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>HDV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,17 +554,17 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>154</v>
       </c>
       <c r="E3" t="n">
-        <v>65.14724637681159</v>
+        <v>29.20720779220779</v>
       </c>
       <c r="F3" t="n">
-        <v>75.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -572,8 +572,16 @@
           <t>2026-08-17T13:32:55.671253+00:00</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:35:49.546017+00:00</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>29.28419999999999</v>
+      </c>
       <c r="K3" t="n">
-        <v>12.08101449275364</v>
+        <v>14.15679999999965</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -584,7 +592,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDV</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -598,17 +606,17 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>154</v>
+        <v>67</v>
       </c>
       <c r="E4" t="n">
-        <v>29.20720779220779</v>
+        <v>65.21807484317543</v>
       </c>
       <c r="F4" t="n">
-        <v>80</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -616,16 +624,8 @@
           <t>2026-08-17T13:32:55.671253+00:00</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-09-08T13:35:49.546017+00:00</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>29.28419999999999</v>
-      </c>
       <c r="K4" t="n">
-        <v>14.15679999999965</v>
+        <v>12.08101449275364</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JEPI</t>
+          <t>HDV</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -513,23 +513,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="E2" t="n">
-        <v>57.355</v>
+        <v>29.20720779220779</v>
       </c>
       <c r="F2" t="n">
-        <v>71.2</v>
+        <v>80</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-04T13:35:33.221049+00:00</t>
-        </is>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:35:49.546017+00:00</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>29.28419999999999</v>
+      </c>
+      <c r="K2" t="n">
+        <v>14.15679999999965</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -540,7 +551,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDV</t>
+          <t>JEPI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,34 +565,23 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="E3" t="n">
-        <v>29.20720779220779</v>
+        <v>57.342585</v>
       </c>
       <c r="F3" t="n">
-        <v>80</v>
+        <v>71.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-17T13:32:55.671253+00:00</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-09-08T13:35:49.546017+00:00</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>29.28419999999999</v>
-      </c>
-      <c r="K3" t="n">
-        <v>14.15679999999965</v>
+          <t>2026-09-04T13:35:33.221049+00:00</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E4" t="n">
         <v>65.21807484317543</v>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>12.08101449275364</v>
+        <v>19.28486480640277</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -551,7 +551,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JEPI</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E3" t="n">
-        <v>57.342585</v>
+        <v>65.21807484317543</v>
       </c>
       <c r="F3" t="n">
-        <v>71.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -580,8 +580,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-04T13:35:33.221049+00:00</t>
-        </is>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>19.28486480640277</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -592,7 +595,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>JEPI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -606,13 +609,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="E4" t="n">
-        <v>65.21807484317543</v>
+        <v>57.342585</v>
       </c>
       <c r="F4" t="n">
-        <v>75.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -621,11 +624,11 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:32:55.671253+00:00</t>
+          <t>2026-09-04T13:35:33.221049+00:00</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>19.28486480640277</v>
+        <v>-0.652585000000002</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
